--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/post DDV_HRM-2031-0180/Panel 7/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/post DDV_HRM-2031-0180/Panel 7/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Back_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,76 +451,81 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Unit 7</t>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.59271</v>
+        <v>17.09969</v>
       </c>
       <c r="D2" t="n">
-        <v>17.07209</v>
+        <v>16.79558</v>
       </c>
       <c r="E2" t="n">
-        <v>16.81497</v>
+        <v>16.95533</v>
       </c>
       <c r="F2" t="n">
-        <v>42.97634</v>
+        <v>42.31501</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05144</v>
+        <v>0.05134</v>
       </c>
       <c r="H2" t="n">
-        <v>1.82306</v>
+        <v>1.84404</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.84016</v>
+        <v>17.13646</v>
       </c>
       <c r="D3" t="n">
-        <v>16.85624</v>
+        <v>16.85919</v>
       </c>
       <c r="E3" t="n">
-        <v>16.83571</v>
+        <v>17.08829</v>
       </c>
       <c r="F3" t="n">
-        <v>43.4</v>
+        <v>43.0448</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05136</v>
+        <v>0.05007</v>
       </c>
       <c r="H3" t="n">
-        <v>1.83743</v>
+        <v>1.82747</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.04951</v>
+        <v>17.16096</v>
       </c>
       <c r="D4" t="n">
-        <v>17.08236</v>
+        <v>16.70564</v>
       </c>
       <c r="E4" t="n">
-        <v>16.74438</v>
+        <v>17.01613</v>
       </c>
       <c r="F4" t="n">
-        <v>43.06024</v>
+        <v>42.79389</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05115</v>
+        <v>0.05028</v>
       </c>
       <c r="H4" t="n">
-        <v>1.86501</v>
+        <v>1.84694</v>
       </c>
     </row>
     <row r="5">
@@ -530,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.05293</v>
+        <v>16.92732</v>
       </c>
       <c r="D5" t="n">
-        <v>16.66811</v>
+        <v>16.67742</v>
       </c>
       <c r="E5" t="n">
-        <v>16.89369</v>
+        <v>16.69705</v>
       </c>
       <c r="F5" t="n">
-        <v>43.00707</v>
+        <v>43.2134</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05069</v>
+        <v>0.05126</v>
       </c>
       <c r="H5" t="n">
-        <v>1.86083</v>
+        <v>1.82615</v>
       </c>
     </row>
     <row r="6">
@@ -555,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.29301</v>
+        <v>17.62542</v>
       </c>
       <c r="D6" t="n">
-        <v>17.20158</v>
+        <v>16.89393</v>
       </c>
       <c r="E6" t="n">
-        <v>16.53541</v>
+        <v>17.03824</v>
       </c>
       <c r="F6" t="n">
-        <v>42.96816</v>
+        <v>43.45375</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04993</v>
+        <v>0.05192</v>
       </c>
       <c r="H6" t="n">
-        <v>1.85184</v>
+        <v>1.84284</v>
       </c>
     </row>
     <row r="7">
@@ -580,359 +585,1596 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.06517</v>
+        <v>17.03183</v>
       </c>
       <c r="D7" t="n">
-        <v>16.74602</v>
+        <v>16.65134</v>
       </c>
       <c r="E7" t="n">
-        <v>17.08154</v>
+        <v>16.9882</v>
       </c>
       <c r="F7" t="n">
-        <v>42.76396</v>
+        <v>43.40429</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05112</v>
+        <v>0.05168</v>
       </c>
       <c r="H7" t="n">
-        <v>1.80598</v>
+        <v>1.83273</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 7</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.92795</v>
+        <v>17.21391</v>
       </c>
       <c r="D8" t="n">
-        <v>16.97705</v>
+        <v>16.64128</v>
       </c>
       <c r="E8" t="n">
-        <v>16.84574</v>
+        <v>16.81692</v>
       </c>
       <c r="F8" t="n">
-        <v>42.80964</v>
+        <v>42.80328</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05145</v>
+        <v>0.0512</v>
       </c>
       <c r="H8" t="n">
-        <v>1.83795</v>
+        <v>1.86125</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.73842</v>
+        <v>17.25557</v>
       </c>
       <c r="D9" t="n">
-        <v>16.89293</v>
+        <v>16.40981</v>
       </c>
       <c r="E9" t="n">
-        <v>16.89036</v>
+        <v>16.68348</v>
       </c>
       <c r="F9" t="n">
-        <v>43.48193</v>
+        <v>43.09661</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05087</v>
+        <v>0.05174</v>
       </c>
       <c r="H9" t="n">
-        <v>1.81247</v>
+        <v>1.86774</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Unit 3</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.72065</v>
+        <v>16.9308</v>
       </c>
       <c r="D10" t="n">
-        <v>16.88389</v>
+        <v>16.73812</v>
       </c>
       <c r="E10" t="n">
-        <v>17.08691</v>
+        <v>16.86935</v>
       </c>
       <c r="F10" t="n">
-        <v>42.97007</v>
+        <v>43.55043</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05089</v>
+        <v>0.04977</v>
       </c>
       <c r="H10" t="n">
-        <v>1.84145</v>
+        <v>1.8361</v>
       </c>
     </row>
     <row r="11">
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Radius</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Unit 10</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>17.05661</v>
+      </c>
+      <c r="D11" t="n">
+        <v>16.74321</v>
+      </c>
+      <c r="E11" t="n">
+        <v>16.93109</v>
+      </c>
+      <c r="F11" t="n">
+        <v>42.39373</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0515</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.82814</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Pad 1</t>
+          <t>Unit 11</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.97049</v>
+        <v>17.11022</v>
       </c>
       <c r="D12" t="n">
-        <v>17.09539</v>
+        <v>16.71553</v>
       </c>
       <c r="E12" t="n">
-        <v>16.76264</v>
+        <v>16.99431</v>
       </c>
       <c r="F12" t="n">
-        <v>41.46092</v>
+        <v>43.39386</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05103</v>
+        <v>0.05083</v>
       </c>
       <c r="H12" t="n">
-        <v>1.8911</v>
+        <v>1.83181</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 12</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17.227</v>
+        <v>17.04997</v>
       </c>
       <c r="D13" t="n">
-        <v>16.87387</v>
+        <v>16.88012</v>
       </c>
       <c r="E13" t="n">
-        <v>16.92835</v>
+        <v>16.98804</v>
       </c>
       <c r="F13" t="n">
-        <v>43.38333</v>
+        <v>42.99314</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05172</v>
+        <v>0.05128</v>
       </c>
       <c r="H13" t="n">
-        <v>1.82303</v>
+        <v>1.85308</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 13</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16.83552</v>
+        <v>17.13286</v>
       </c>
       <c r="D14" t="n">
-        <v>17.03058</v>
+        <v>16.62296</v>
       </c>
       <c r="E14" t="n">
-        <v>17.17379</v>
+        <v>16.69566</v>
       </c>
       <c r="F14" t="n">
-        <v>43.09674</v>
+        <v>42.62819</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05194</v>
+        <v>0.05001</v>
       </c>
       <c r="H14" t="n">
-        <v>1.85166</v>
+        <v>1.81052</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 14</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16.87177</v>
+        <v>17.04353</v>
       </c>
       <c r="D15" t="n">
-        <v>17.11854</v>
+        <v>16.78375</v>
       </c>
       <c r="E15" t="n">
-        <v>16.82871</v>
+        <v>16.83849</v>
       </c>
       <c r="F15" t="n">
-        <v>43.20617</v>
+        <v>43.4265</v>
       </c>
       <c r="G15" t="n">
-        <v>0.051</v>
+        <v>0.05213</v>
       </c>
       <c r="H15" t="n">
-        <v>1.83228</v>
+        <v>1.85959</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 15</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.05969</v>
+        <v>17.11381</v>
       </c>
       <c r="D16" t="n">
-        <v>16.77506</v>
+        <v>16.77218</v>
       </c>
       <c r="E16" t="n">
-        <v>16.98743</v>
+        <v>17.03211</v>
       </c>
       <c r="F16" t="n">
-        <v>43.54111</v>
+        <v>43.23584</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05197</v>
+        <v>0.05077</v>
       </c>
       <c r="H16" t="n">
-        <v>1.85567</v>
+        <v>1.85693</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 16</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.00023</v>
+        <v>16.89958</v>
       </c>
       <c r="D17" t="n">
-        <v>16.70605</v>
+        <v>16.54545</v>
       </c>
       <c r="E17" t="n">
-        <v>17.08471</v>
+        <v>16.6477</v>
       </c>
       <c r="F17" t="n">
-        <v>43.8228</v>
+        <v>43.97198</v>
       </c>
       <c r="G17" t="n">
-        <v>0.05134</v>
+        <v>0.05202</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8547</v>
+        <v>1.81819</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 17</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17.29567</v>
+        <v>17.01065</v>
       </c>
       <c r="D18" t="n">
-        <v>16.70573</v>
+        <v>16.80733</v>
       </c>
       <c r="E18" t="n">
-        <v>16.71952</v>
+        <v>17.01024</v>
       </c>
       <c r="F18" t="n">
-        <v>43.2804</v>
+        <v>42.40709</v>
       </c>
       <c r="G18" t="n">
-        <v>0.05107</v>
+        <v>0.05085</v>
       </c>
       <c r="H18" t="n">
-        <v>1.80974</v>
+        <v>1.85888</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 18</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>17.13072</v>
+        <v>17.18309</v>
       </c>
       <c r="D19" t="n">
-        <v>16.49763</v>
+        <v>16.94356</v>
       </c>
       <c r="E19" t="n">
-        <v>16.81717</v>
+        <v>17.16533</v>
       </c>
       <c r="F19" t="n">
-        <v>42.65885</v>
+        <v>43.1887</v>
       </c>
       <c r="G19" t="n">
-        <v>0.04989</v>
+        <v>0.05187</v>
       </c>
       <c r="H19" t="n">
-        <v>1.85613</v>
+        <v>1.8312</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Unit 19</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>17.37663</v>
+      </c>
+      <c r="D20" t="n">
+        <v>16.50409</v>
+      </c>
+      <c r="E20" t="n">
+        <v>16.82729</v>
+      </c>
+      <c r="F20" t="n">
+        <v>42.86829</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.05187</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.85667</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Unit 20</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>17.16346</v>
+      </c>
+      <c r="D21" t="n">
+        <v>16.66069</v>
+      </c>
+      <c r="E21" t="n">
+        <v>16.83309</v>
+      </c>
+      <c r="F21" t="n">
+        <v>42.52252</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.05049</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.82072</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Unit 21</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>17.35731</v>
+      </c>
+      <c r="D22" t="n">
+        <v>16.70049</v>
+      </c>
+      <c r="E22" t="n">
+        <v>16.78718</v>
+      </c>
+      <c r="F22" t="n">
+        <v>42.72613</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.05059</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.8438</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Unit 22</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>17.05911</v>
+      </c>
+      <c r="D23" t="n">
+        <v>16.34177</v>
+      </c>
+      <c r="E23" t="n">
+        <v>16.84878</v>
+      </c>
+      <c r="F23" t="n">
+        <v>42.32881</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.05064</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.82091</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Unit 23</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>16.99256</v>
+      </c>
+      <c r="D24" t="n">
+        <v>16.71412</v>
+      </c>
+      <c r="E24" t="n">
+        <v>16.85061</v>
+      </c>
+      <c r="F24" t="n">
+        <v>42.91591</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.05101</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.82502</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Unit 24</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>17.16094</v>
+      </c>
+      <c r="D25" t="n">
+        <v>16.67706</v>
+      </c>
+      <c r="E25" t="n">
+        <v>16.96387</v>
+      </c>
+      <c r="F25" t="n">
+        <v>42.36748</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.05042</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.81943</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Unit 25</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>17.19596</v>
+      </c>
+      <c r="D26" t="n">
+        <v>16.76546</v>
+      </c>
+      <c r="E26" t="n">
+        <v>16.7887</v>
+      </c>
+      <c r="F26" t="n">
+        <v>43.06595</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.05131</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.81516</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unit 26</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>16.92461</v>
+      </c>
+      <c r="D27" t="n">
+        <v>16.76881</v>
+      </c>
+      <c r="E27" t="n">
+        <v>16.87858</v>
+      </c>
+      <c r="F27" t="n">
+        <v>43.30085</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.05186</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.83121</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Unit 27</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>16.76952</v>
+      </c>
+      <c r="D28" t="n">
+        <v>16.62</v>
+      </c>
+      <c r="E28" t="n">
+        <v>16.65982</v>
+      </c>
+      <c r="F28" t="n">
+        <v>43.33708</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.05027</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.85413</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unit 28</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>17.24424</v>
+      </c>
+      <c r="D29" t="n">
+        <v>16.86265</v>
+      </c>
+      <c r="E29" t="n">
+        <v>17.19762</v>
+      </c>
+      <c r="F29" t="n">
+        <v>43.34655</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.05075</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.81735</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unit 29</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>16.94052</v>
+      </c>
+      <c r="D30" t="n">
+        <v>16.63198</v>
+      </c>
+      <c r="E30" t="n">
+        <v>16.65627</v>
+      </c>
+      <c r="F30" t="n">
+        <v>43.30423</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.05147</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.81452</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unit 30</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>16.8892</v>
+      </c>
+      <c r="D31" t="n">
+        <v>16.50835</v>
+      </c>
+      <c r="E31" t="n">
+        <v>16.6845</v>
+      </c>
+      <c r="F31" t="n">
+        <v>43.03426</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.05072</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.80873</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 31</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>17.26141</v>
+      </c>
+      <c r="D32" t="n">
+        <v>16.24235</v>
+      </c>
+      <c r="E32" t="n">
+        <v>17.05353</v>
+      </c>
+      <c r="F32" t="n">
+        <v>42.35888</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.05139</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.81914</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 32</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>17.40303</v>
+      </c>
+      <c r="D33" t="n">
+        <v>16.78504</v>
+      </c>
+      <c r="E33" t="n">
+        <v>16.825</v>
+      </c>
+      <c r="F33" t="n">
+        <v>42.92961</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.05025</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.85668</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 33</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>16.96004</v>
+      </c>
+      <c r="D34" t="n">
+        <v>16.84597</v>
+      </c>
+      <c r="E34" t="n">
+        <v>16.92517</v>
+      </c>
+      <c r="F34" t="n">
+        <v>43.0172</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.05189</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.83287</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 34</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>17.18191</v>
+      </c>
+      <c r="D35" t="n">
+        <v>16.6731</v>
+      </c>
+      <c r="E35" t="n">
+        <v>16.88488</v>
+      </c>
+      <c r="F35" t="n">
+        <v>43.07418</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.05198</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.81745</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 35</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>17.15745</v>
+      </c>
+      <c r="D36" t="n">
+        <v>16.64692</v>
+      </c>
+      <c r="E36" t="n">
+        <v>16.81639</v>
+      </c>
+      <c r="F36" t="n">
+        <v>43.13319</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.05056</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.82984</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 36</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>17.08292</v>
+      </c>
+      <c r="D37" t="n">
+        <v>16.63693</v>
+      </c>
+      <c r="E37" t="n">
+        <v>16.87988</v>
+      </c>
+      <c r="F37" t="n">
+        <v>43.34801</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.05075</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.84404</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Trace 1</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>16.9986</v>
+      </c>
+      <c r="D39" t="n">
+        <v>16.22305</v>
+      </c>
+      <c r="E39" t="n">
+        <v>16.78018</v>
+      </c>
+      <c r="F39" t="n">
+        <v>21.91805</v>
+      </c>
+      <c r="G39" t="n">
+        <v>34.08604</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>17.2032</v>
+      </c>
+      <c r="D40" t="n">
+        <v>16.27998</v>
+      </c>
+      <c r="E40" t="n">
+        <v>16.75413</v>
+      </c>
+      <c r="F40" t="n">
+        <v>22.01117</v>
+      </c>
+      <c r="G40" t="n">
+        <v>34.66175</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>16.89196</v>
-      </c>
-      <c r="D20" t="n">
-        <v>16.72336</v>
-      </c>
-      <c r="E20" t="n">
-        <v>16.77616</v>
-      </c>
-      <c r="F20" t="n">
-        <v>42.62606</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.0514</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1.81661</v>
+      <c r="C41" t="n">
+        <v>17.28465</v>
+      </c>
+      <c r="D41" t="n">
+        <v>16.3751</v>
+      </c>
+      <c r="E41" t="n">
+        <v>16.67868</v>
+      </c>
+      <c r="F41" t="n">
+        <v>22.33491</v>
+      </c>
+      <c r="G41" t="n">
+        <v>34.88251</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>16.97142</v>
+      </c>
+      <c r="D42" t="n">
+        <v>16.27921</v>
+      </c>
+      <c r="E42" t="n">
+        <v>16.50671</v>
+      </c>
+      <c r="F42" t="n">
+        <v>22.12761</v>
+      </c>
+      <c r="G42" t="n">
+        <v>34.07991</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>16.95487</v>
+      </c>
+      <c r="D43" t="n">
+        <v>16.17093</v>
+      </c>
+      <c r="E43" t="n">
+        <v>16.6339</v>
+      </c>
+      <c r="F43" t="n">
+        <v>21.94618</v>
+      </c>
+      <c r="G43" t="n">
+        <v>35.23894</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>16.82948</v>
+      </c>
+      <c r="D44" t="n">
+        <v>15.93411</v>
+      </c>
+      <c r="E44" t="n">
+        <v>16.55597</v>
+      </c>
+      <c r="F44" t="n">
+        <v>21.9341</v>
+      </c>
+      <c r="G44" t="n">
+        <v>34.20774</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>16.74285</v>
+      </c>
+      <c r="D45" t="n">
+        <v>16.2634</v>
+      </c>
+      <c r="E45" t="n">
+        <v>16.51777</v>
+      </c>
+      <c r="F45" t="n">
+        <v>21.9796</v>
+      </c>
+      <c r="G45" t="n">
+        <v>34.75648</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>17.10318</v>
+      </c>
+      <c r="D46" t="n">
+        <v>15.9693</v>
+      </c>
+      <c r="E46" t="n">
+        <v>16.08117</v>
+      </c>
+      <c r="F46" t="n">
+        <v>22.23318</v>
+      </c>
+      <c r="G46" t="n">
+        <v>34.51133</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>16.99298</v>
+      </c>
+      <c r="D47" t="n">
+        <v>16.3953</v>
+      </c>
+      <c r="E47" t="n">
+        <v>16.43883</v>
+      </c>
+      <c r="F47" t="n">
+        <v>22.00249</v>
+      </c>
+      <c r="G47" t="n">
+        <v>35.13506</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unit 10</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>17.31825</v>
+      </c>
+      <c r="D48" t="n">
+        <v>16.16143</v>
+      </c>
+      <c r="E48" t="n">
+        <v>16.66961</v>
+      </c>
+      <c r="F48" t="n">
+        <v>21.9934</v>
+      </c>
+      <c r="G48" t="n">
+        <v>35.0574</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unit 11</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>16.9762</v>
+      </c>
+      <c r="D49" t="n">
+        <v>16.17568</v>
+      </c>
+      <c r="E49" t="n">
+        <v>16.42069</v>
+      </c>
+      <c r="F49" t="n">
+        <v>21.79556</v>
+      </c>
+      <c r="G49" t="n">
+        <v>34.38941</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unit 12</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>16.78632</v>
+      </c>
+      <c r="D50" t="n">
+        <v>16.50612</v>
+      </c>
+      <c r="E50" t="n">
+        <v>16.77682</v>
+      </c>
+      <c r="F50" t="n">
+        <v>21.83297</v>
+      </c>
+      <c r="G50" t="n">
+        <v>34.52228</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Unit 13</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>16.96645</v>
+      </c>
+      <c r="D51" t="n">
+        <v>16.25601</v>
+      </c>
+      <c r="E51" t="n">
+        <v>16.66275</v>
+      </c>
+      <c r="F51" t="n">
+        <v>22.32649</v>
+      </c>
+      <c r="G51" t="n">
+        <v>33.69247</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unit 14</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>16.83266</v>
+      </c>
+      <c r="D52" t="n">
+        <v>16.1672</v>
+      </c>
+      <c r="E52" t="n">
+        <v>16.47563</v>
+      </c>
+      <c r="F52" t="n">
+        <v>21.80707</v>
+      </c>
+      <c r="G52" t="n">
+        <v>35.40556</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unit 15</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>16.96175</v>
+      </c>
+      <c r="D53" t="n">
+        <v>16.39864</v>
+      </c>
+      <c r="E53" t="n">
+        <v>16.69548</v>
+      </c>
+      <c r="F53" t="n">
+        <v>21.37868</v>
+      </c>
+      <c r="G53" t="n">
+        <v>34.53583</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unit 16</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>17.0885</v>
+      </c>
+      <c r="D54" t="n">
+        <v>16.09875</v>
+      </c>
+      <c r="E54" t="n">
+        <v>16.55216</v>
+      </c>
+      <c r="F54" t="n">
+        <v>22.15013</v>
+      </c>
+      <c r="G54" t="n">
+        <v>34.25142</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unit 17</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>16.82151</v>
+      </c>
+      <c r="D55" t="n">
+        <v>15.74415</v>
+      </c>
+      <c r="E55" t="n">
+        <v>16.13017</v>
+      </c>
+      <c r="F55" t="n">
+        <v>22.11384</v>
+      </c>
+      <c r="G55" t="n">
+        <v>34.9454</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unit 18</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>16.88372</v>
+      </c>
+      <c r="D56" t="n">
+        <v>16.18117</v>
+      </c>
+      <c r="E56" t="n">
+        <v>16.76013</v>
+      </c>
+      <c r="F56" t="n">
+        <v>21.6996</v>
+      </c>
+      <c r="G56" t="n">
+        <v>34.25607</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unit 19</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>17.25151</v>
+      </c>
+      <c r="D57" t="n">
+        <v>16.33342</v>
+      </c>
+      <c r="E57" t="n">
+        <v>16.55268</v>
+      </c>
+      <c r="F57" t="n">
+        <v>21.85867</v>
+      </c>
+      <c r="G57" t="n">
+        <v>34.16235</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unit 20</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>17.10411</v>
+      </c>
+      <c r="D58" t="n">
+        <v>16.16454</v>
+      </c>
+      <c r="E58" t="n">
+        <v>16.71244</v>
+      </c>
+      <c r="F58" t="n">
+        <v>22.26162</v>
+      </c>
+      <c r="G58" t="n">
+        <v>33.86559</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unit 21</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>16.68818</v>
+      </c>
+      <c r="D59" t="n">
+        <v>16.09614</v>
+      </c>
+      <c r="E59" t="n">
+        <v>16.45361</v>
+      </c>
+      <c r="F59" t="n">
+        <v>22.29204</v>
+      </c>
+      <c r="G59" t="n">
+        <v>34.75339</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unit 22</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>16.66359</v>
+      </c>
+      <c r="D60" t="n">
+        <v>16.27063</v>
+      </c>
+      <c r="E60" t="n">
+        <v>16.48308</v>
+      </c>
+      <c r="F60" t="n">
+        <v>22.02606</v>
+      </c>
+      <c r="G60" t="n">
+        <v>34.44657</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Unit 23</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>17.12999</v>
+      </c>
+      <c r="D61" t="n">
+        <v>16.09703</v>
+      </c>
+      <c r="E61" t="n">
+        <v>16.80184</v>
+      </c>
+      <c r="F61" t="n">
+        <v>21.7688</v>
+      </c>
+      <c r="G61" t="n">
+        <v>34.91035</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unit 24</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>17.15004</v>
+      </c>
+      <c r="D62" t="n">
+        <v>16.44544</v>
+      </c>
+      <c r="E62" t="n">
+        <v>16.80084</v>
+      </c>
+      <c r="F62" t="n">
+        <v>22.04274</v>
+      </c>
+      <c r="G62" t="n">
+        <v>34.61685</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unit 25</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>16.7657</v>
+      </c>
+      <c r="D63" t="n">
+        <v>16.42466</v>
+      </c>
+      <c r="E63" t="n">
+        <v>16.53073</v>
+      </c>
+      <c r="F63" t="n">
+        <v>22.0124</v>
+      </c>
+      <c r="G63" t="n">
+        <v>34.45018</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unit 26</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>16.64212</v>
+      </c>
+      <c r="D64" t="n">
+        <v>16.13823</v>
+      </c>
+      <c r="E64" t="n">
+        <v>16.47904</v>
+      </c>
+      <c r="F64" t="n">
+        <v>21.80767</v>
+      </c>
+      <c r="G64" t="n">
+        <v>34.38053</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unit 27</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>17.05572</v>
+      </c>
+      <c r="D65" t="n">
+        <v>15.92542</v>
+      </c>
+      <c r="E65" t="n">
+        <v>16.6276</v>
+      </c>
+      <c r="F65" t="n">
+        <v>22.38955</v>
+      </c>
+      <c r="G65" t="n">
+        <v>34.51254</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unit 28</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>16.50924</v>
+      </c>
+      <c r="D66" t="n">
+        <v>16.4475</v>
+      </c>
+      <c r="E66" t="n">
+        <v>16.49276</v>
+      </c>
+      <c r="F66" t="n">
+        <v>21.99979</v>
+      </c>
+      <c r="G66" t="n">
+        <v>34.77456</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unit 29</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>16.71141</v>
+      </c>
+      <c r="D67" t="n">
+        <v>16.02859</v>
+      </c>
+      <c r="E67" t="n">
+        <v>16.65068</v>
+      </c>
+      <c r="F67" t="n">
+        <v>21.93744</v>
+      </c>
+      <c r="G67" t="n">
+        <v>34.92667</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unit 30</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>16.94957</v>
+      </c>
+      <c r="D68" t="n">
+        <v>16.12854</v>
+      </c>
+      <c r="E68" t="n">
+        <v>16.63868</v>
+      </c>
+      <c r="F68" t="n">
+        <v>22.39456</v>
+      </c>
+      <c r="G68" t="n">
+        <v>34.30061</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unit 31</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>16.91652</v>
+      </c>
+      <c r="D69" t="n">
+        <v>16.16481</v>
+      </c>
+      <c r="E69" t="n">
+        <v>16.78507</v>
+      </c>
+      <c r="F69" t="n">
+        <v>22.08663</v>
+      </c>
+      <c r="G69" t="n">
+        <v>34.35257</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Unit 32</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>16.89369</v>
+      </c>
+      <c r="D70" t="n">
+        <v>16.17885</v>
+      </c>
+      <c r="E70" t="n">
+        <v>16.42213</v>
+      </c>
+      <c r="F70" t="n">
+        <v>22.22656</v>
+      </c>
+      <c r="G70" t="n">
+        <v>35.21107</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Unit 33</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>17.30647</v>
+      </c>
+      <c r="D71" t="n">
+        <v>15.8339</v>
+      </c>
+      <c r="E71" t="n">
+        <v>16.57343</v>
+      </c>
+      <c r="F71" t="n">
+        <v>21.46917</v>
+      </c>
+      <c r="G71" t="n">
+        <v>34.77353</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Unit 34</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>16.96237</v>
+      </c>
+      <c r="D72" t="n">
+        <v>16.13336</v>
+      </c>
+      <c r="E72" t="n">
+        <v>16.77097</v>
+      </c>
+      <c r="F72" t="n">
+        <v>21.89107</v>
+      </c>
+      <c r="G72" t="n">
+        <v>34.5583</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Unit 35</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>16.77002</v>
+      </c>
+      <c r="D73" t="n">
+        <v>16.11215</v>
+      </c>
+      <c r="E73" t="n">
+        <v>16.55477</v>
+      </c>
+      <c r="F73" t="n">
+        <v>21.95051</v>
+      </c>
+      <c r="G73" t="n">
+        <v>34.45157</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Unit 36</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>16.97812</v>
+      </c>
+      <c r="D74" t="n">
+        <v>16.13313</v>
+      </c>
+      <c r="E74" t="n">
+        <v>16.33508</v>
+      </c>
+      <c r="F74" t="n">
+        <v>22.14621</v>
+      </c>
+      <c r="G74" t="n">
+        <v>34.59964</v>
       </c>
     </row>
   </sheetData>
